--- a/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
+++ b/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>27</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>124</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(4355, 5)   (Matrix: progScrollText("I Wanna Dance With Somebody by Whitney Houston", 24435, 80, getRandomColor(), 14))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4355, 5)   (Matrix: progScrollText("I Wanna Dance With Somebody by Whitney Houston", 24435, 80, getRandomColor(), 14))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>strobo</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(726, 10, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(726, 10, 100, getRandomCRGB())</t>
         </is>
@@ -572,13 +593,19 @@
           <t>intro</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(17419, 6, 12)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progPalette(17419, 6, 12)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>strobo</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 14, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 14, 100, getRandomCRGB())</t>
         </is>
@@ -614,13 +647,19 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(15484, 16, 480, true)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15484, 16, 480, true)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>ive done alright</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(11613, 18, 30)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(11613, 18, 30)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>übergang chorus</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 20, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 20, 100, getRandomCRGB())</t>
         </is>
@@ -677,13 +728,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13548, 1925, 22, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 22, 5, 26, 5, false, 4)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>w. smbdy who loves me</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 24, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 24, 100, getRandomCRGB())</t>
         </is>
@@ -719,13 +782,19 @@
           <t>chorus 1 weiter</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13548, 1925, 26, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 26, 5, 26, 5, true, 3)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>w. smbdy who loves me</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1935, 6, 28)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 6, 28)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>stehender chord</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 30, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 30, 100, getRandomCRGB())</t>
         </is>
@@ -782,13 +863,19 @@
           <t>übergang verse</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixHorizontal(1935, 32, 70, true)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(1935, 32, 70, true)</t>
         </is>
@@ -803,13 +890,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(15484, 34, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15484, 34, 50, true, false)</t>
         </is>
@@ -824,13 +917,19 @@
           <t>ive done alright</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(11613, 9, 36)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progPalette(11613, 9, 36)</t>
         </is>
@@ -845,13 +944,19 @@
           <t>übergang chorus</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 38, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 38, 100, getRandomCRGB())</t>
         </is>
@@ -866,13 +971,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13548, 1925, 40, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -887,13 +998,19 @@
           <t>w. smbdy who loves me</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1935, 6, 42)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 6, 42)</t>
         </is>
@@ -908,13 +1025,19 @@
           <t>chorus 2 weiter</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13548, 1925, 44, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 44, 5, 26, 5, true, 3)</t>
         </is>
@@ -929,13 +1052,19 @@
           <t>w. smbdy who loves me</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 46, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 46, 100, getRandomCRGB())</t>
         </is>
@@ -950,13 +1079,19 @@
           <t>Say you wanna dance</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(13548, 6, 48)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13548, 6, 48)</t>
         </is>
@@ -971,13 +1106,19 @@
           <t>übergang</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixHorizontal(1935, 50, 70, true)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(1935, 50, 70, true)</t>
         </is>
@@ -992,13 +1133,19 @@
           <t>i need a man …</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(11613, 12, 52)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>progPalette(11613, 12, 52)</t>
         </is>
@@ -1013,13 +1160,19 @@
           <t>übergang chorus</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 54, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 54, 100, getRandomCRGB())</t>
         </is>
@@ -1034,13 +1187,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13548, 964, 56, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 964, 56, 5, 26, 5, false, 4)</t>
         </is>
@@ -1055,13 +1214,19 @@
           <t>w. smbdy who loves me</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 58, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 58, 100, getRandomCRGB())</t>
         </is>
@@ -1076,13 +1241,19 @@
           <t>chorus 3 weiter</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13548, 480, 60, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 480, 60, 5, 26, 5, true, 3)</t>
         </is>
@@ -1097,13 +1268,19 @@
           <t>w. smbdy who loves me</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 62, 100, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 62, 100, getRandomCRGB())</t>
         </is>
@@ -1118,13 +1295,19 @@
           <t>Say you wanna dance</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(2661, 64, 120, true)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 64, 120, true)</t>
         </is>
@@ -1139,13 +1322,19 @@
           <t>strobe</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1210, 4, 66)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 4, 66)</t>
         </is>
@@ -1160,13 +1349,19 @@
           <t>Say you wanna dance</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(2661, 68, 120, true)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 68, 120, true)</t>
         </is>
@@ -1181,13 +1376,19 @@
           <t>strobe</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1210, 6, 70)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 6, 70)</t>
         </is>
@@ -1202,13 +1403,19 @@
           <t>Say you wanna dance</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(2661, 72, 120, true)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 72, 120, true)</t>
         </is>
@@ -1223,13 +1430,19 @@
           <t>strobe</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1210, 8, 74)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 8, 74)</t>
         </is>
@@ -1244,13 +1457,19 @@
           <t>w. some…</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(1935, 480, 76, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(1935, 480, 76, 5, 26, 5, false, 4)</t>
         </is>
@@ -1265,13 +1484,19 @@
           <t>...bdy who loves me</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1935, 10, 78)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 10, 78)</t>
         </is>
@@ -1291,10 +1516,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
+++ b/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>2.625</v>
+        <v>3.625</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>109.375</v>
+        <v>110.375</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>111.375</v>
+        <v>112.375</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>113.375</v>
+        <v>114.375</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>

--- a/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
+++ b/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>27</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>124</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4355, 5)   (Matrix: progScrollText("I Wanna Dance With Somebody by Whitney Houston", 24435, 80, getRandomColor(), 14))</t>
         </is>
@@ -573,12 +583,13 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(726, 10, 100, getRandomCRGB())</t>
         </is>
@@ -600,12 +611,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, NEON, pumpt im Beat (pulse 40) - statt weißer Wellen.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progPalette(17419, 6, 12)</t>
         </is>
@@ -627,12 +643,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Buildup (1 Takt), NEON: lädt sich auf, Explosion auf den Gesangseinsatz.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 14, 100, getRandomCRGB())</t>
         </is>
@@ -654,12 +675,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, NEON: dezenter Puls im Beat.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15484, 16, 480, true)</t>
         </is>
@@ -681,12 +707,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, SUNSET, darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 6 Takte). Fester Look für beide "ive done alright".</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(11613, 18, 30)</t>
         </is>
@@ -708,12 +739,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Weißer Strobo statt Zufallsfarbe. Gilt für alle drei "übergang chorus".</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 20, 100, getRandomCRGB())</t>
         </is>
@@ -735,12 +771,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, in NEON mit weichen Farbwechseln (soft 40), Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 22, 5, 26, 5, false, 4)</t>
         </is>
@@ -762,12 +803,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Hook-Motiv: Szene Drop, WHITE (Schläge auf die Viertel), auf der Matrix "LOVES ME" über der Szene. Bei allen sechs gleich, dazwischen farbig (RED), beim ersten und letzten Mal weiß.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 24, 100, getRandomCRGB())</t>
         </is>
@@ -789,12 +835,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Stern, NEON, Lampen blitzen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 26, 5, 26, 5, true, 3)</t>
         </is>
@@ -816,12 +867,13 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 6, 28)</t>
         </is>
@@ -843,12 +895,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Blinder springt auf die 1 (Takt 45) und klingt über den ganzen Takt aus, darunter Schwarz.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 30, 100, getRandomCRGB())</t>
         </is>
@@ -870,12 +927,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Leuchtspuren bleiben, weich eingeblendet.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(1935, 32, 70, true)</t>
         </is>
@@ -897,12 +959,17 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Szene Rain, SUNSET, Farbwanderung (triad, 2 Takte) - anderer Look als verse 1.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15484, 34, 50, true, false)</t>
         </is>
@@ -924,12 +991,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal (Palette SUNSET + Glitzern).</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progPalette(11613, 9, 36)</t>
         </is>
@@ -951,12 +1023,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 38, 100, getRandomCRGB())</t>
         </is>
@@ -978,12 +1051,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Stern, NEON, Blinder auf den Einsatz, Lampen-Backbeat.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -1005,12 +1083,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 6, 42)</t>
         </is>
@@ -1032,12 +1111,13 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 44, 5, 26, 5, true, 3)</t>
         </is>
@@ -1059,12 +1139,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 46, 100, getRandomCRGB())</t>
         </is>
@@ -1086,12 +1167,17 @@
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, NEON: Bühnenhälften blitzen abwechselnd - "say you wanna dance" als Frage und Antwort. Auf der Matrix "DANCE" im Beat.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13548, 6, 48)</t>
         </is>
@@ -1113,12 +1199,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(1935, 50, 70, true)</t>
         </is>
@@ -1140,12 +1227,17 @@
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip, ROYAL: stehende Helix auf der Matrix, alle anderen pulsieren einmal je Takt (bisher Palette 12, die es nicht gibt - zeigt die zuletzt geladene).</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>progPalette(11613, 12, 52)</t>
         </is>
@@ -1167,12 +1259,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 54, 100, getRandomCRGB())</t>
         </is>
@@ -1194,12 +1287,17 @@
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, SUNSET - eine Stufe wärmer; Blinder auf den Einsatz.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 964, 56, 5, 26, 5, false, 4)</t>
         </is>
@@ -1221,12 +1319,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 58, 100, getRandomCRGB())</t>
         </is>
@@ -1248,12 +1347,17 @@
         </is>
       </c>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, FIRE, Lampen-Backbeat.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 480, 60, 5, 26, 5, true, 3)</t>
         </is>
@@ -1275,12 +1379,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 62, 100, getRandomCRGB())</t>
         </is>
@@ -1302,12 +1407,17 @@
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Call Response wie oben, jetzt in FIRE. Gilt für (2), (3), (4).</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 64, 120, true)</t>
         </is>
@@ -1329,12 +1439,17 @@
         </is>
       </c>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Kurzer starker Blinder statt Einzelblitzen (auf den Schlag voll, klingt bis zum Part-Ende ab). Gilt für alle drei, jedes Mal etwas länger voll.</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 4, 66)</t>
         </is>
@@ -1356,12 +1471,13 @@
         </is>
       </c>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 68, 120, true)</t>
         </is>
@@ -1383,12 +1499,13 @@
         </is>
       </c>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 6, 70)</t>
         </is>
@@ -1410,12 +1527,13 @@
         </is>
       </c>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 72, 120, true)</t>
         </is>
@@ -1437,12 +1555,13 @@
         </is>
       </c>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 8, 74)</t>
         </is>
@@ -1464,12 +1583,17 @@
         </is>
       </c>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Stern in WHITE, Text "SOMEBODY" auf der Matrix.</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(1935, 480, 76, 5, 26, 5, false, 4)</t>
         </is>
@@ -1491,12 +1615,17 @@
         </is>
       </c>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Hook-Motiv zum letzten Mal in Weiß mit Glitzern; starker Blinder auf der letzten Viertel (Takt 116,75), klingt 5 Sekunden ins Schluss-Schwarz aus (wie APT.).</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 10, 78)</t>
         </is>
@@ -1516,10 +1645,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
+++ b/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>progBlack(4355, 5)
+          <t>progBlack(4355, 3)
 Alles schwarz bis zum Einsatz (die Matrix zeigt den Titel-Lauftext).</t>
         </is>
       </c>
@@ -578,7 +578,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(726, 10, 100, getRandomCRGB())
+          <t>progStrobo(726, 4, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -606,7 +606,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>progPalette(17419, 6, 15)
+          <t>progPalette(17419, 6, 5)
 Alter Effekt: weiße Wellen, weich an- und abschwellend.</t>
         </is>
       </c>
@@ -638,7 +638,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1935, 20, 100, getRandomCRGB())
+          <t>progStrobo(1935, 6, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -670,7 +670,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(15484, 25, 484, true)
+          <t>progRandomLines(15484, 7, 484, true)
 Alter Effekt: pro Beat eine neue zufällige Linie in Zufallsfarbe.</t>
         </is>
       </c>
@@ -702,7 +702,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>progMatrixScanner(11613, 30, 30)
+          <t>progMatrixScanner(11613, 8, 30)
 Alter Effekt: ruhiger Scanner, eine Leuchtlinie fährt hin und her.</t>
         </is>
       </c>
@@ -734,7 +734,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1936, 35, 100, getRandomCRGB())
+          <t>progStrobo(1936, 9, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -766,7 +766,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13548, 1935, 40, 5, 26, 5, false, 4)
+          <t>progSternNeu(13548, 1935, 10, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel jeden Takt.</t>
         </is>
       </c>
@@ -798,7 +798,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1936, 45, 100, getRandomCRGB())
+          <t>progStrobo(1936, 11, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -830,7 +830,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13548, 1935, 50, 5, 26, 5, true, 3)
+          <t>progSternNeu(13548, 1935, 12, 5, 26, 5, true, 3)
 Alter Effekt: drehender, wandernder Stern, Farbwechsel jeden Takt.</t>
         </is>
       </c>
@@ -862,7 +862,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1935, 6, 55)
+          <t>progFastBlingBling(1935, 6, 13)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>
@@ -890,7 +890,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1936, 60, 100, getRandomCRGB())
+          <t>progStrobo(1936, 14, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -922,7 +922,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>progMatrixHorizontal(1935, 65, 70, true)
+          <t>progMatrixHorizontal(1935, 15, 70, true)
 Alter Effekt: 1 Takt Leuchtspuren, die nach Weiß aufhellen.</t>
         </is>
       </c>
@@ -954,7 +954,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>progWaterRipple(15484, 70, 50, true, false)
+          <t>progWaterRipple(15484, 16, 50, true, false)
 Alter Effekt: Wasserringe an zufälligen Stellen, mit Farbverlauf.</t>
         </is>
       </c>
@@ -986,7 +986,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>progPalette(11613, 9, 75)
+          <t>progPalette(11613, 9, 17)
 Alter Effekt: rot-weiß-blaue Blöcke mit Lücken, harte Kanten.</t>
         </is>
       </c>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1936, 80, 100, getRandomCRGB())
+          <t>progStrobo(1936, 18, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13548, 1935, 85, 5, 26, 5, false, 4)
+          <t>progSternNeu(13548, 1935, 19, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel jeden Takt.</t>
         </is>
       </c>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1936, 6, 90)
+          <t>progFastBlingBling(1936, 6, 20)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13548, 1935, 95, 5, 26, 5, true, 3)
+          <t>progSternNeu(13548, 1935, 21, 5, 26, 5, true, 3)
 Alter Effekt: drehender, wandernder Stern, Farbwechsel jeden Takt.</t>
         </is>
       </c>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1935, 100, 100, getRandomCRGB())
+          <t>progStrobo(1935, 22, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(13549, 6, 105)
+          <t>progFastBlingBling(13549, 6, 23)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>progMatrixHorizontal(1935, 110, 70, true)
+          <t>progMatrixHorizontal(1935, 24, 70, true)
 Alter Effekt: 1 Takt Leuchtspuren, die nach Weiß aufhellen.</t>
         </is>
       </c>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>progPalette(11613, 12, 115)
+          <t>progPalette(11613, 12, 25)
 Alter Effekt: Farbband mit Palette 12. Diese Palette ist im Code nicht definiert - zu sehen ist die zuletzt geladene (hier die rot-weiß-blaue aus "ive done alright").</t>
         </is>
       </c>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1936, 120, 100, getRandomCRGB())
+          <t>progStrobo(1936, 26, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe. Ab hier (transponierter Teil) sind die Bund-Marker 1 und 4 aus.</t>
         </is>
       </c>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13548, 968, 125, 5, 26, 5, false, 4)
+          <t>progSternNeu(13548, 968, 27, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel alle 2 Beats.</t>
         </is>
       </c>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1936, 130, 100, getRandomCRGB())
+          <t>progStrobo(1936, 28, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13548, 484, 135, 5, 26, 5, true, 3)
+          <t>progSternNeu(13548, 484, 29, 5, 26, 5, true, 3)
 Alter Effekt: drehender, wandernder Stern, Farbwechsel pro Beat.</t>
         </is>
       </c>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1935, 140, 100, getRandomCRGB())
+          <t>progStrobo(1935, 30, 100, getRandomCRGB())
 Alter Effekt: harter Strobo (100 ms) in Zufallsfarbe.</t>
         </is>
       </c>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(2662, 145, 120, true)
+          <t>progRandomLines(2662, 31, 120, true)
 Alter Effekt: sehr schnell wechselnde zufällige Linien (alle 120 ms, eine Sechzehntel).</t>
         </is>
       </c>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1209, 4, 150)
+          <t>progFastBlingBling(1209, 4, 32)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(2662, 155, 120, true)
+          <t>progRandomLines(2662, 33, 120, true)
 Alter Effekt: sehr schnell wechselnde zufällige Linien (alle 120 ms, eine Sechzehntel).</t>
         </is>
       </c>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1209, 6, 160)
+          <t>progFastBlingBling(1209, 6, 34)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(2662, 165, 120, true)
+          <t>progRandomLines(2662, 35, 120, true)
 Alter Effekt: sehr schnell wechselnde zufällige Linien (alle 120 ms, eine Sechzehntel).</t>
         </is>
       </c>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1209, 8, 170)
+          <t>progFastBlingBling(1209, 8, 36)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(1936, 484, 175, 5, 26, 5, false, 4)
+          <t>progSternNeu(1936, 484, 37, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel pro Beat.</t>
         </is>
       </c>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1935, 10, 180)
+          <t>progFastBlingBling(1935, 10, 38)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>

--- a/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
+++ b/songs/IWannaDanceWithSomebody_v1/quelle/struktur.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,6 +39,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -71,6 +77,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,17 +445,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +482,7 @@
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -484,6 +495,7 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -496,6 +508,7 @@
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -515,25 +528,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Neuer Vorschlag (KI)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -556,12 +574,13 @@
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4355, 5)   (Matrix: progScrollText("I Wanna Dance With Somebody by Whitney Houston", 24435, 80, getRandomColor(), 14))</t>
         </is>
@@ -584,12 +603,13 @@
       </c>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(726, 10, 100, getRandomCRGB())</t>
         </is>
@@ -611,17 +631,18 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Szene Palette, NEON, pumpt im Beat (pulse 40) - statt weißer Wellen.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>progPalette(17419, 6, 12)</t>
         </is>
@@ -643,17 +664,18 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Szene Buildup (1 Takt), NEON: lädt sich auf, Explosion auf den Gesangseinsatz.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 14, 100, getRandomCRGB())</t>
         </is>
@@ -668,24 +690,30 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_SUNSET
+Strophe neu (18.10.2026, statt der alten Zufallslinien): dezent im Beat - Zonen der Gitarre, Lichtschuss in den Lampen, Sinuswellen im Takt auf der Matrix, warme Farben</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15484, 7, 484, true)
 Alter Effekt: pro Beat eine neue zufällige Linie in Zufallsfarbe.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Szene Verse, NEON: dezenter Puls im Beat.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15484, 16, 480, true)</t>
         </is>
@@ -707,17 +735,18 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Szene Palette, SUNSET, darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 6 Takte). Fester Look für beide "ive done alright".</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(11613, 18, 30)</t>
         </is>
@@ -739,17 +768,18 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Weißer Strobo statt Zufallsfarbe. Gilt für alle drei "übergang chorus".</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 20, 100, getRandomCRGB())</t>
         </is>
@@ -771,17 +801,18 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Stern bleibt, in NEON mit weichen Farbwechseln (soft 40), Blinder auf den Einsatz (2 Beats).</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 22, 5, 26, 5, false, 4)</t>
         </is>
@@ -803,17 +834,18 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Hook-Motiv: Szene Drop, WHITE (Schläge auf die Viertel), auf der Matrix "LOVES ME" über der Szene. Bei allen sechs gleich, dazwischen farbig (RED), beim ersten und letzten Mal weiß.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 24, 100, getRandomCRGB())</t>
         </is>
@@ -835,17 +867,18 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Stern, NEON, Lampen blitzen weiß auf 2 und 4.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 26, 5, 26, 5, true, 3)</t>
         </is>
@@ -868,12 +901,13 @@
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 6, 28)</t>
         </is>
@@ -895,17 +929,18 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Blinder springt auf die 1 (Takt 45) und klingt über den ganzen Takt aus, darunter Schwarz.</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 30, 100, getRandomCRGB())</t>
         </is>
@@ -927,17 +962,18 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Leuchtspuren bleiben, weich eingeblendet.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(1935, 32, 70, true)</t>
         </is>
@@ -952,24 +988,30 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_NEON
+Strophe neu (18.10.2026, statt der alten Wasserringe): 'somebody who loves me' - alle Geräte schlagen auf jedem Beat wie ein Herz in Pink/Cyan/Violett, die Matrix zeigt eine Lissajous-Schleife</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15484, 16, 50, true, false)
 Alter Effekt: Wasserringe an zufälligen Stellen, mit Farbverlauf.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Szene Rain, SUNSET, Farbwanderung (triad, 2 Takte) - anderer Look als verse 1.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15484, 34, 50, true, false)</t>
         </is>
@@ -991,17 +1033,18 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>wie beim ersten Mal (Palette SUNSET + Glitzern).</t>
         </is>
       </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>progPalette(11613, 9, 36)</t>
         </is>
@@ -1024,12 +1067,13 @@
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 38, 100, getRandomCRGB())</t>
         </is>
@@ -1051,17 +1095,18 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Stern, NEON, Blinder auf den Einsatz, Lampen-Backbeat.</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -1084,12 +1129,13 @@
       </c>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 6, 42)</t>
         </is>
@@ -1112,12 +1158,13 @@
       </c>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 1925, 44, 5, 26, 5, true, 3)</t>
         </is>
@@ -1140,12 +1187,13 @@
       </c>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 46, 100, getRandomCRGB())</t>
         </is>
@@ -1167,17 +1215,18 @@
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Szene Call Response, NEON: Bühnenhälften blitzen abwechselnd - "say you wanna dance" als Frage und Antwort. Auf der Matrix "DANCE" im Beat.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13548, 6, 48)</t>
         </is>
@@ -1200,12 +1249,13 @@
       </c>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(1935, 50, 70, true)</t>
         </is>
@@ -1227,17 +1277,18 @@
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Szene DNA Flip, ROYAL: stehende Helix auf der Matrix, alle anderen pulsieren einmal je Takt (bisher Palette 12, die es nicht gibt - zeigt die zuletzt geladene).</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>progPalette(11613, 12, 52)</t>
         </is>
@@ -1260,12 +1311,13 @@
       </c>
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 54, 100, getRandomCRGB())</t>
         </is>
@@ -1287,17 +1339,18 @@
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Szene Star, SUNSET - eine Stufe wärmer; Blinder auf den Einsatz.</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 964, 56, 5, 26, 5, false, 4)</t>
         </is>
@@ -1320,12 +1373,13 @@
       </c>
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 58, 100, getRandomCRGB())</t>
         </is>
@@ -1347,17 +1401,18 @@
         </is>
       </c>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Szene Star, FIRE, Lampen-Backbeat.</t>
         </is>
       </c>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13548, 480, 60, 5, 26, 5, true, 3)</t>
         </is>
@@ -1380,12 +1435,13 @@
       </c>
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 62, 100, getRandomCRGB())</t>
         </is>
@@ -1407,17 +1463,18 @@
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Call Response wie oben, jetzt in FIRE. Gilt für (2), (3), (4).</t>
         </is>
       </c>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 64, 120, true)</t>
         </is>
@@ -1439,17 +1496,18 @@
         </is>
       </c>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Kurzer starker Blinder statt Einzelblitzen (auf den Schlag voll, klingt bis zum Part-Ende ab). Gilt für alle drei, jedes Mal etwas länger voll.</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 4, 66)</t>
         </is>
@@ -1472,12 +1530,13 @@
       </c>
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 68, 120, true)</t>
         </is>
@@ -1500,12 +1559,13 @@
       </c>
       <c r="D37" s="6" t="n"/>
       <c r="E37" s="6" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 6, 70)</t>
         </is>
@@ -1528,12 +1588,13 @@
       </c>
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(2661, 72, 120, true)</t>
         </is>
@@ -1556,12 +1617,13 @@
       </c>
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1210, 8, 74)</t>
         </is>
@@ -1583,17 +1645,18 @@
         </is>
       </c>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>Stern in WHITE, Text "SOMEBODY" auf der Matrix.</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(1935, 480, 76, 5, 26, 5, false, 4)</t>
         </is>
@@ -1615,17 +1678,18 @@
         </is>
       </c>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Hook-Motiv zum letzten Mal in Weiß mit Glitzern; starker Blinder auf der letzten Viertel (Takt 116,75), klingt 5 Sekunden ins Schluss-Schwarz aus (wie APT.).</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1935, 10, 78)</t>
         </is>
@@ -1645,10 +1709,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <f>$C$3</f>
         <v/>
       </c>
